--- a/output/CS_SFIAFormat/sfiaformat_mapping_cosine_SkillNER QE_KeyBERT_CS.xlsx
+++ b/output/CS_SFIAFormat/sfiaformat_mapping_cosine_SkillNER QE_KeyBERT_CS.xlsx
@@ -502,7 +502,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0.2902</v>
+        <v>0.4606</v>
       </c>
       <c r="H3" t="n">
         <v>0.2184</v>
@@ -523,10 +523,10 @@
         <v>0.2945</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2659</v>
+        <v>0.4107</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2278</v>
+        <v>0.2863</v>
       </c>
       <c r="H4" t="n">
         <v>0.3033</v>
@@ -543,10 +543,10 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0.2163</v>
+        <v>0.2512</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2562</v>
+        <v>0.2781</v>
       </c>
       <c r="H5" t="n">
         <v>0.2422</v>
@@ -562,7 +562,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>0.2451</v>
+        <v>0.2849</v>
       </c>
       <c r="F6" t="n">
         <v>0.2589</v>
@@ -586,7 +586,7 @@
         <v>0.2095</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2537</v>
+        <v>0.3011</v>
       </c>
       <c r="H7" t="n">
         <v>0.3596</v>
@@ -605,10 +605,10 @@
         <v>0.2792</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2153</v>
+        <v>0.2906</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2184</v>
+        <v>0.2339</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -727,7 +727,7 @@
         <v>0.3404</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2647</v>
+        <v>0.3158</v>
       </c>
       <c r="E15" t="n">
         <v>0.2912</v>
@@ -749,7 +749,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.2294</v>
+        <v>0.2343</v>
       </c>
       <c r="E16" t="n">
         <v>0.2204</v>
@@ -776,7 +776,7 @@
         <v>0.3744</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2127</v>
+        <v>0.2648</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -798,7 +798,7 @@
         <v>0.2507</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2461</v>
+        <v>0.2589</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -810,20 +810,20 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>0.2989</v>
+        <v>0.3639</v>
       </c>
       <c r="D19" t="n">
         <v>0.2636</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3421</v>
+        <v>0.3514</v>
       </c>
       <c r="F19" t="n">
         <v>0.2048</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.2366</v>
+        <v>0.2618</v>
       </c>
     </row>
     <row r="20">
@@ -837,17 +837,17 @@
         <v>0.2585</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2005</v>
+        <v>0.2313</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2689</v>
+        <v>0.2841</v>
       </c>
       <c r="F20" t="n">
         <v>0.2725</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.2508</v>
+        <v>0.2989</v>
       </c>
     </row>
     <row r="21">
@@ -877,14 +877,14 @@
         <v>0.2287</v>
       </c>
       <c r="D22" t="n">
-        <v>0.227</v>
+        <v>0.2451</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
         <v>0.235</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2345</v>
+        <v>0.2578</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>0.2237</v>
+        <v>0.2829</v>
       </c>
       <c r="D23" t="n">
         <v>0.2456</v>
@@ -936,22 +936,22 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>0.3131</v>
+        <v>0.3857</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2378</v>
+        <v>0.2783</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3062</v>
+        <v>0.3457</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2259</v>
+        <v>0.2805</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2568</v>
+        <v>0.2709</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2381</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="26">
@@ -972,7 +972,7 @@
         <v>0.2811</v>
       </c>
       <c r="G26" t="n">
-        <v>0.323</v>
+        <v>0.4195</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -996,10 +996,10 @@
         <v>0.2014</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2239</v>
+        <v>0.4341</v>
       </c>
       <c r="H27" t="n">
-        <v>0.273</v>
+        <v>0.2752</v>
       </c>
     </row>
     <row r="28">
@@ -1016,7 +1016,7 @@
         <v>0.3568</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3257</v>
+        <v>0.3296</v>
       </c>
       <c r="F28" t="n">
         <v>0.2339</v>
@@ -1056,16 +1056,16 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>0.2479</v>
+        <v>0.2598</v>
       </c>
       <c r="F30" t="n">
         <v>0.2488</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2479</v>
+        <v>0.4039</v>
       </c>
       <c r="H30" t="n">
-        <v>0.382</v>
+        <v>0.3915</v>
       </c>
     </row>
     <row r="31">
@@ -1078,13 +1078,13 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>0.2291</v>
+        <v>0.2427</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2638</v>
+        <v>0.3455</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2096</v>
+        <v>0.2703</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>0.2816</v>
+        <v>0.3105</v>
       </c>
       <c r="D32" t="n">
         <v>0.255</v>
@@ -1121,10 +1121,10 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.219</v>
+        <v>0.2762</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2454</v>
+        <v>0.2849</v>
       </c>
       <c r="H33" t="n">
         <v>0.2257</v>
@@ -1159,7 +1159,7 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>0.2156</v>
+        <v>0.2219</v>
       </c>
     </row>
     <row r="36">
@@ -1180,7 +1180,7 @@
         <v>0.2015</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2222</v>
+        <v>0.2854</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1222,7 +1222,7 @@
         <v>0.2126</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2054</v>
+        <v>0.2251</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1236,11 +1236,11 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>0.2143</v>
+        <v>0.2423</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>0.3434</v>
+        <v>0.3995</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>0.2624</v>
+        <v>0.3605</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
@@ -1296,7 +1296,7 @@
         <v>0.2437</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2262</v>
+        <v>0.2362</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>0.2004</v>
+        <v>0.3188</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
@@ -1321,7 +1321,7 @@
         <v>0.2182</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2007</v>
+        <v>0.2151</v>
       </c>
     </row>
     <row r="44">
@@ -1337,7 +1337,7 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>0.2692</v>
+        <v>0.3553</v>
       </c>
     </row>
     <row r="45">
@@ -1349,13 +1349,13 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>0.2258</v>
+        <v>0.4127</v>
       </c>
       <c r="E45" t="n">
-        <v>0.242</v>
+        <v>0.5135</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2019</v>
+        <v>0.2502</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -1393,7 +1393,7 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
-        <v>0.2468</v>
+        <v>0.3452</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
@@ -1432,13 +1432,13 @@
         <v>0.2635</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2427</v>
+        <v>0.3852</v>
       </c>
       <c r="F49" t="n">
         <v>0.2292</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2129</v>
+        <v>0.2261</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1456,7 +1456,7 @@
         <v>0.307</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2371</v>
+        <v>0.2736</v>
       </c>
       <c r="H50" t="n">
         <v>0.2079</v>
@@ -1479,7 +1479,7 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>0.2066</v>
+        <v>0.3102</v>
       </c>
     </row>
     <row r="52">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.2141</v>
+        <v>0.2566</v>
       </c>
       <c r="D52" t="n">
         <v>0.2069</v>
@@ -1499,7 +1499,7 @@
         <v>0.3539</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2056</v>
+        <v>0.2438</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
@@ -1512,17 +1512,17 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0.2105</v>
+        <v>0.3321</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2254</v>
+        <v>0.3389</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>0.2226</v>
+        <v>0.3586</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2221</v>
+        <v>0.2718</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1534,16 +1534,16 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>0.2192</v>
+        <v>0.3141</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2171</v>
+        <v>0.2854</v>
       </c>
       <c r="E54" t="n">
         <v>0.2466</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2582</v>
+        <v>0.3292</v>
       </c>
       <c r="G54" t="n">
         <v>0.2505</v>
@@ -1561,16 +1561,16 @@
         <v>0.3304</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2542</v>
+        <v>0.3806</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2203</v>
+        <v>0.2926</v>
       </c>
       <c r="F55" t="n">
         <v>0.2818</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2051</v>
+        <v>0.2115</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>0.2012</v>
+        <v>0.3004</v>
       </c>
       <c r="D56" t="n">
         <v>0.2205</v>
@@ -1606,16 +1606,16 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>0.3163</v>
+        <v>0.4653</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2137</v>
+        <v>0.452</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2141</v>
+        <v>0.4709</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2506</v>
+        <v>0.3076</v>
       </c>
       <c r="G57" t="n">
         <v>0.3355</v>
@@ -1663,7 +1663,7 @@
         <v>0.2486</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2235</v>
+        <v>0.2633</v>
       </c>
       <c r="G59" t="n">
         <v>0.2096</v>
@@ -1680,7 +1680,7 @@
         <v>0.3395</v>
       </c>
       <c r="C60" t="n">
-        <v>0.2338</v>
+        <v>0.3366</v>
       </c>
       <c r="D60" t="n">
         <v>0.2067</v>
@@ -1720,13 +1720,13 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0.2407</v>
+        <v>0.2538</v>
       </c>
       <c r="D62" t="n">
-        <v>0.2178</v>
+        <v>0.3381</v>
       </c>
       <c r="E62" t="n">
-        <v>0.2079</v>
+        <v>0.3359</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>0.2193</v>
+        <v>0.2991</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
@@ -1756,19 +1756,19 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>0.21</v>
+        <v>0.2169</v>
       </c>
       <c r="D64" t="n">
-        <v>0.2026</v>
+        <v>0.2232</v>
       </c>
       <c r="E64" t="n">
         <v>0.2111</v>
       </c>
       <c r="F64" t="n">
-        <v>0.2049</v>
+        <v>0.2228</v>
       </c>
       <c r="G64" t="n">
-        <v>0.2637</v>
+        <v>0.3345</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -1788,7 +1788,7 @@
         <v>0.362</v>
       </c>
       <c r="G65" t="n">
-        <v>0.258</v>
+        <v>0.3406</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>0.2014</v>
+        <v>0.2807</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -1840,17 +1840,17 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0.2009</v>
+        <v>0.2559</v>
       </c>
       <c r="D68" t="n">
-        <v>0.219</v>
+        <v>0.2245</v>
       </c>
       <c r="E68" t="n">
         <v>0.2008</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>0.227</v>
+        <v>0.2342</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -1862,13 +1862,13 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>0.2782</v>
+        <v>0.3196</v>
       </c>
       <c r="D69" t="n">
         <v>0.253</v>
       </c>
       <c r="E69" t="n">
-        <v>0.251</v>
+        <v>0.2639</v>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
@@ -1882,16 +1882,16 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>0.2039</v>
+        <v>0.2349</v>
       </c>
       <c r="D70" t="n">
-        <v>0.2295</v>
+        <v>0.3266</v>
       </c>
       <c r="E70" t="n">
         <v>0.2328</v>
       </c>
       <c r="F70" t="n">
-        <v>0.2166</v>
+        <v>0.2629</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
@@ -1904,11 +1904,11 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>0.2004</v>
+        <v>0.306</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>0.2205</v>
+        <v>0.2336</v>
       </c>
       <c r="F71" t="n">
         <v>0.2343</v>
@@ -1927,16 +1927,16 @@
         <v>0.3181</v>
       </c>
       <c r="D72" t="n">
-        <v>0.266</v>
+        <v>0.4174</v>
       </c>
       <c r="E72" t="n">
         <v>0.2476</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2011</v>
+        <v>0.231</v>
       </c>
       <c r="G72" t="n">
-        <v>0.2051</v>
+        <v>0.2057</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -1948,16 +1948,16 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>0.2103</v>
+        <v>0.2406</v>
       </c>
       <c r="D73" t="n">
         <v>0.2041</v>
       </c>
       <c r="E73" t="n">
-        <v>0.2205</v>
+        <v>0.2345</v>
       </c>
       <c r="F73" t="n">
-        <v>0.2651</v>
+        <v>0.3575</v>
       </c>
       <c r="G73" t="n">
         <v>0.2055</v>
@@ -1979,7 +1979,7 @@
         <v>0.3166</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2204</v>
+        <v>0.2904</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
@@ -1992,19 +1992,19 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>0.2582</v>
+        <v>0.4358</v>
       </c>
       <c r="D75" t="n">
         <v>0.3731</v>
       </c>
       <c r="E75" t="n">
-        <v>0.2262</v>
+        <v>0.3556</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2175</v>
+        <v>0.2458</v>
       </c>
       <c r="G75" t="n">
-        <v>0.2105</v>
+        <v>0.2473</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2017,10 +2017,10 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="n">
-        <v>0.2094</v>
+        <v>0.3956</v>
       </c>
       <c r="E76" t="n">
-        <v>0.2118</v>
+        <v>0.2568</v>
       </c>
       <c r="F76" t="n">
         <v>0.2338</v>
@@ -2037,7 +2037,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
-        <v>0.2435</v>
+        <v>0.3318</v>
       </c>
       <c r="E77" t="n">
         <v>0.2001</v>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>0.2029</v>
+        <v>0.3093</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>0.211</v>
+        <v>0.261</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>0.2249</v>
+        <v>0.2517</v>
       </c>
       <c r="D79" t="n">
         <v>0.2373</v>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>0.2935</v>
+        <v>0.3596</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>0.2552</v>
+        <v>0.2854</v>
       </c>
       <c r="D81" t="n">
         <v>0.2169</v>
@@ -2138,10 +2138,10 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>0.2049</v>
+        <v>0.2213</v>
       </c>
       <c r="D82" t="n">
-        <v>0.2043</v>
+        <v>0.2921</v>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
@@ -2158,11 +2158,11 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>0.2184</v>
+        <v>0.4733</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>0.2278</v>
+        <v>0.3565</v>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
@@ -2184,7 +2184,7 @@
         <v>0.237</v>
       </c>
       <c r="E84" t="n">
-        <v>0.2028</v>
+        <v>0.2255</v>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
@@ -2200,10 +2200,10 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>0.2065</v>
+        <v>0.2361</v>
       </c>
       <c r="D85" t="n">
-        <v>0.2227</v>
+        <v>0.2491</v>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.2933</v>
+        <v>0.3138</v>
       </c>
       <c r="C86" t="n">
         <v>0.2104</v>
@@ -2233,7 +2233,7 @@
         <v>0.2111</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2564</v>
+        <v>0.3445</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
@@ -2249,7 +2249,7 @@
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
-        <v>0.2492</v>
+        <v>0.274</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
@@ -2284,16 +2284,16 @@
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
-        <v>0.2103</v>
+        <v>0.3466</v>
       </c>
       <c r="F89" t="n">
-        <v>0.2073</v>
+        <v>0.3648</v>
       </c>
       <c r="G89" t="n">
         <v>0.4584</v>
       </c>
       <c r="H89" t="n">
-        <v>0.298</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="90">
@@ -2307,13 +2307,13 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>0.3548</v>
+        <v>0.4551</v>
       </c>
       <c r="G90" t="n">
         <v>0.2515</v>
       </c>
       <c r="H90" t="n">
-        <v>0.2405</v>
+        <v>0.2521</v>
       </c>
     </row>
     <row r="91">
@@ -2324,16 +2324,16 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>0.2095</v>
+        <v>0.4126</v>
       </c>
       <c r="D91" t="n">
-        <v>0.2237</v>
+        <v>0.2659</v>
       </c>
       <c r="E91" t="n">
-        <v>0.2988</v>
+        <v>0.3217</v>
       </c>
       <c r="F91" t="n">
-        <v>0.2165</v>
+        <v>0.2622</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
@@ -2348,7 +2348,7 @@
         <v>0.2377</v>
       </c>
       <c r="C92" t="n">
-        <v>0.2243</v>
+        <v>0.2862</v>
       </c>
       <c r="D92" t="n">
         <v>0.2124</v>
@@ -2371,7 +2371,7 @@
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="n">
-        <v>0.2207</v>
+        <v>0.2275</v>
       </c>
       <c r="E93" t="n">
         <v>0.2636</v>
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.2328</v>
+        <v>0.4048</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2153</v>
+        <v>0.3178</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2037</v>
+        <v>0.2915</v>
       </c>
       <c r="E94" t="n">
         <v>0.2915</v>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.2707</v>
+        <v>0.3619</v>
       </c>
       <c r="C95" t="n">
-        <v>0.2153</v>
+        <v>0.2475</v>
       </c>
       <c r="D95" t="n">
         <v>0.2579</v>
@@ -2421,7 +2421,7 @@
         <v>0.2496</v>
       </c>
       <c r="F95" t="n">
-        <v>0.261</v>
+        <v>0.3831</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
@@ -2434,19 +2434,19 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>0.2001</v>
+        <v>0.2466</v>
       </c>
       <c r="D96" t="n">
         <v>0.233</v>
       </c>
       <c r="E96" t="n">
-        <v>0.2315</v>
+        <v>0.2857</v>
       </c>
       <c r="F96" t="n">
         <v>0.2242</v>
       </c>
       <c r="G96" t="n">
-        <v>0.2319</v>
+        <v>0.3243</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2459,13 +2459,13 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
-        <v>0.2017</v>
+        <v>0.2351</v>
       </c>
       <c r="E97" t="n">
         <v>0.2269</v>
       </c>
       <c r="F97" t="n">
-        <v>0.2238</v>
+        <v>0.2293</v>
       </c>
       <c r="G97" t="n">
         <v>0.2791</v>
@@ -2481,16 +2481,16 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="n">
-        <v>0.3069</v>
+        <v>0.3515</v>
       </c>
       <c r="E98" t="n">
-        <v>0.2162</v>
+        <v>0.2561</v>
       </c>
       <c r="F98" t="n">
         <v>0.2314</v>
       </c>
       <c r="G98" t="n">
-        <v>0.2115</v>
+        <v>0.3485</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2502,19 +2502,19 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>0.3076</v>
+        <v>0.3078</v>
       </c>
       <c r="D99" t="n">
-        <v>0.2022</v>
+        <v>0.2594</v>
       </c>
       <c r="E99" t="n">
-        <v>0.2514</v>
+        <v>0.2789</v>
       </c>
       <c r="F99" t="n">
-        <v>0.222</v>
+        <v>0.3373</v>
       </c>
       <c r="G99" t="n">
-        <v>0.2807</v>
+        <v>0.3432</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>0.2088</v>
+        <v>0.233</v>
       </c>
       <c r="D100" t="n">
         <v>0.3568</v>
@@ -2535,7 +2535,7 @@
         <v>0.216</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2039</v>
+        <v>0.2291</v>
       </c>
       <c r="G100" t="n">
         <v>0.2049</v>
@@ -2550,22 +2550,22 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>0.2419</v>
+        <v>0.3256</v>
       </c>
       <c r="D101" t="n">
-        <v>0.2137</v>
+        <v>0.3124</v>
       </c>
       <c r="E101" t="n">
-        <v>0.2513</v>
+        <v>0.3185</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2268</v>
+        <v>0.2959</v>
       </c>
       <c r="G101" t="n">
-        <v>0.2086</v>
+        <v>0.2526</v>
       </c>
       <c r="H101" t="n">
-        <v>0.2452</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="102">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="n">
-        <v>0.2095</v>
+        <v>0.2549</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
@@ -2595,7 +2595,7 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>0.2198</v>
+        <v>0.2674</v>
       </c>
       <c r="E103" t="n">
         <v>0.3852</v>
@@ -2604,7 +2604,7 @@
         <v>0.2444</v>
       </c>
       <c r="G103" t="n">
-        <v>0.3746</v>
+        <v>0.4474</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -2622,7 +2622,7 @@
         <v>0.2204</v>
       </c>
       <c r="E104" t="n">
-        <v>0.2116</v>
+        <v>0.2136</v>
       </c>
       <c r="F104" t="n">
         <v>0.2814</v>
@@ -2650,7 +2650,7 @@
         <v>0.2241</v>
       </c>
       <c r="G105" t="n">
-        <v>0.2117</v>
+        <v>0.2261</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2668,10 +2668,10 @@
         <v>0.2162</v>
       </c>
       <c r="E106" t="n">
-        <v>0.2646</v>
+        <v>0.2885</v>
       </c>
       <c r="F106" t="n">
-        <v>0.2163</v>
+        <v>0.2522</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
@@ -2685,13 +2685,13 @@
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="n">
-        <v>0.2793</v>
+        <v>0.2929</v>
       </c>
       <c r="E107" t="n">
         <v>0.3526</v>
       </c>
       <c r="F107" t="n">
-        <v>0.2325</v>
+        <v>0.2505</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
@@ -2704,10 +2704,10 @@
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
-        <v>0.2382</v>
+        <v>0.2481</v>
       </c>
       <c r="D108" t="n">
-        <v>0.2382</v>
+        <v>0.2481</v>
       </c>
       <c r="E108" t="n">
         <v>0.2524</v>
@@ -2724,10 +2724,10 @@
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>0.2196</v>
+        <v>0.2325</v>
       </c>
       <c r="D109" t="n">
-        <v>0.213</v>
+        <v>0.2354</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
@@ -2745,13 +2745,13 @@
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>0.2023</v>
+        <v>0.2381</v>
       </c>
       <c r="E110" t="n">
-        <v>0.3227</v>
+        <v>0.3436</v>
       </c>
       <c r="F110" t="n">
-        <v>0.267</v>
+        <v>0.2888</v>
       </c>
       <c r="G110" t="n">
         <v>0.2242</v>
@@ -2765,16 +2765,16 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.2028</v>
+        <v>0.2997</v>
       </c>
       <c r="C111" t="n">
         <v>0.2147</v>
       </c>
       <c r="D111" t="n">
-        <v>0.2793</v>
+        <v>0.2979</v>
       </c>
       <c r="E111" t="n">
-        <v>0.2952</v>
+        <v>0.3159</v>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
@@ -2789,19 +2789,19 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.2195</v>
+        <v>0.2764</v>
       </c>
       <c r="C112" t="n">
-        <v>0.2176</v>
+        <v>0.4266</v>
       </c>
       <c r="D112" t="n">
-        <v>0.3487</v>
+        <v>0.3865</v>
       </c>
       <c r="E112" t="n">
-        <v>0.28</v>
+        <v>0.3285</v>
       </c>
       <c r="F112" t="n">
-        <v>0.256</v>
+        <v>0.2567</v>
       </c>
       <c r="G112" t="n">
         <v>0.2508</v>
@@ -2819,13 +2819,13 @@
         <v>0.2981</v>
       </c>
       <c r="D113" t="n">
-        <v>0.2149</v>
+        <v>0.2645</v>
       </c>
       <c r="E113" t="n">
         <v>0.3076</v>
       </c>
       <c r="F113" t="n">
-        <v>0.2147</v>
+        <v>0.2525</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
-        <v>0.2121</v>
+        <v>0.241</v>
       </c>
       <c r="D114" t="n">
         <v>0.2214</v>
@@ -2878,19 +2878,19 @@
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
-        <v>0.2406</v>
+        <v>0.4472</v>
       </c>
       <c r="D116" t="n">
-        <v>0.2752</v>
+        <v>0.3139</v>
       </c>
       <c r="E116" t="n">
-        <v>0.2372</v>
+        <v>0.2567</v>
       </c>
       <c r="F116" t="n">
-        <v>0.2615</v>
+        <v>0.3177</v>
       </c>
       <c r="G116" t="n">
-        <v>0.216</v>
+        <v>0.3358</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>0.2671</v>
+        <v>0.3082</v>
       </c>
       <c r="D117" t="n">
         <v>0.2204</v>
@@ -2911,7 +2911,7 @@
         <v>0.2014</v>
       </c>
       <c r="F117" t="n">
-        <v>0.2641</v>
+        <v>0.2856</v>
       </c>
       <c r="G117" t="n">
         <v>0.2716</v>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.2013</v>
+        <v>0.292</v>
       </c>
       <c r="C118" t="n">
         <v>0.2158</v>
@@ -2955,7 +2955,7 @@
         <v>0.3502</v>
       </c>
       <c r="F119" t="n">
-        <v>0.2036</v>
+        <v>0.2569</v>
       </c>
       <c r="G119" t="n">
         <v>0.2546</v>
@@ -2974,7 +2974,7 @@
         <v>0.206</v>
       </c>
       <c r="E120" t="n">
-        <v>0.2173</v>
+        <v>0.2618</v>
       </c>
       <c r="F120" t="n">
         <v>0.2141</v>
@@ -2992,10 +2992,10 @@
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="n">
-        <v>0.2579</v>
+        <v>0.5393</v>
       </c>
       <c r="F121" t="n">
-        <v>0.2791</v>
+        <v>0.3083</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
@@ -3010,7 +3010,7 @@
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="n">
-        <v>0.2169</v>
+        <v>0.4022</v>
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
@@ -3031,7 +3031,7 @@
         <v>0.3523</v>
       </c>
       <c r="F123" t="n">
-        <v>0.2055</v>
+        <v>0.3245</v>
       </c>
       <c r="G123" t="n">
         <v>0.3229</v>
@@ -3048,13 +3048,13 @@
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="n">
-        <v>0.2413</v>
+        <v>0.317</v>
       </c>
       <c r="F124" t="n">
         <v>0.3186</v>
       </c>
       <c r="G124" t="n">
-        <v>0.2913</v>
+        <v>0.3259</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3083,7 +3083,7 @@
         <v>0.2574</v>
       </c>
       <c r="D126" t="n">
-        <v>0.226</v>
+        <v>0.2811</v>
       </c>
       <c r="E126" t="n">
         <v>0.2096</v>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
-        <v>0.218</v>
+        <v>0.2518</v>
       </c>
       <c r="D127" t="n">
         <v>0.2047</v>
@@ -3115,7 +3115,7 @@
         <v>0.2345</v>
       </c>
       <c r="H127" t="n">
-        <v>0.2039</v>
+        <v>0.2332</v>
       </c>
     </row>
     <row r="128">
@@ -3130,7 +3130,7 @@
         <v>0.3238</v>
       </c>
       <c r="E128" t="n">
-        <v>0.2297</v>
+        <v>0.2356</v>
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
@@ -3167,13 +3167,13 @@
         <v>0.3251</v>
       </c>
       <c r="D130" t="n">
-        <v>0.2248</v>
+        <v>0.2276</v>
       </c>
       <c r="E130" t="n">
         <v>0.2559</v>
       </c>
       <c r="F130" t="n">
-        <v>0.2455</v>
+        <v>0.2652</v>
       </c>
       <c r="G130" t="n">
         <v>0.2956</v>
@@ -3188,13 +3188,13 @@
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
-        <v>0.2054</v>
+        <v>0.2485</v>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>0.2236</v>
+        <v>0.2318</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3207,19 +3207,19 @@
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="n">
-        <v>0.2126</v>
+        <v>0.2649</v>
       </c>
       <c r="E132" t="n">
         <v>0.2195</v>
       </c>
       <c r="F132" t="n">
-        <v>0.3107</v>
+        <v>0.322</v>
       </c>
       <c r="G132" t="n">
-        <v>0.2501</v>
+        <v>0.2744</v>
       </c>
       <c r="H132" t="n">
-        <v>0.2329</v>
+        <v>0.3085</v>
       </c>
     </row>
     <row r="133">
@@ -3236,7 +3236,7 @@
         <v>0.204</v>
       </c>
       <c r="G133" t="n">
-        <v>0.3005</v>
+        <v>0.4585</v>
       </c>
       <c r="H133" t="n">
         <v>0.2599</v>
@@ -3255,7 +3255,7 @@
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>0.2052</v>
+        <v>0.2248</v>
       </c>
     </row>
     <row r="135">
@@ -3267,7 +3267,7 @@
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="n">
-        <v>0.2067</v>
+        <v>0.2549</v>
       </c>
       <c r="E135" t="n">
         <v>0.2034</v>
@@ -3275,7 +3275,7 @@
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>0.2062</v>
+        <v>0.2599</v>
       </c>
     </row>
     <row r="136">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="n">
-        <v>0.2791</v>
+        <v>0.3782</v>
       </c>
       <c r="D136" t="n">
         <v>0.2087</v>
@@ -3296,7 +3296,7 @@
         <v>0.2458</v>
       </c>
       <c r="G136" t="n">
-        <v>0.2167</v>
+        <v>0.262</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>0.2779</v>
+        <v>0.2841</v>
       </c>
     </row>
     <row r="138">
@@ -3330,19 +3330,19 @@
         <v>0.2693</v>
       </c>
       <c r="C138" t="n">
-        <v>0.2076</v>
+        <v>0.2901</v>
       </c>
       <c r="D138" t="n">
-        <v>0.2223</v>
+        <v>0.2755</v>
       </c>
       <c r="E138" t="n">
         <v>0.2834</v>
       </c>
       <c r="F138" t="n">
-        <v>0.3226</v>
+        <v>0.4534</v>
       </c>
       <c r="G138" t="n">
-        <v>0.2484</v>
+        <v>0.4532</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3353,22 +3353,22 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.2683</v>
+        <v>0.3081</v>
       </c>
       <c r="C139" t="n">
         <v>0.2073</v>
       </c>
       <c r="D139" t="n">
-        <v>0.2334</v>
+        <v>0.2381</v>
       </c>
       <c r="E139" t="n">
-        <v>0.2242</v>
+        <v>0.3766</v>
       </c>
       <c r="F139" t="n">
-        <v>0.3188</v>
+        <v>0.3853</v>
       </c>
       <c r="G139" t="n">
-        <v>0.2207</v>
+        <v>0.3187</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="n">
-        <v>0.212</v>
+        <v>0.318</v>
       </c>
       <c r="G140" t="n">
         <v>0.2238</v>
@@ -3421,20 +3421,20 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.2001</v>
+        <v>0.4391</v>
       </c>
       <c r="C142" t="n">
-        <v>0.2926</v>
+        <v>0.3243</v>
       </c>
       <c r="D142" t="n">
-        <v>0.3714</v>
+        <v>0.4914</v>
       </c>
       <c r="E142" t="n">
-        <v>0.2495</v>
+        <v>0.3721</v>
       </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="n">
-        <v>0.201</v>
+        <v>0.5808</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3461,13 +3461,13 @@
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
-        <v>0.2323</v>
+        <v>0.45</v>
       </c>
       <c r="E144" t="n">
         <v>0.2003</v>
       </c>
       <c r="F144" t="n">
-        <v>0.2119</v>
+        <v>0.3919</v>
       </c>
       <c r="G144" t="n">
         <v>0.2013</v>
@@ -3484,10 +3484,10 @@
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="n">
-        <v>0.2182</v>
+        <v>0.2606</v>
       </c>
       <c r="F145" t="n">
-        <v>0.224</v>
+        <v>0.2265</v>
       </c>
       <c r="G145" t="n">
         <v>0.2648</v>
@@ -3519,7 +3519,7 @@
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="n">
-        <v>0.2376</v>
+        <v>0.2399</v>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
